--- a/data/trans_orig/IP11C$ingresado-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP11C$ingresado-Estudios-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,04%</t>
         </is>
       </c>
     </row>
@@ -944,112 +944,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -1057,112 +1057,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>674</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
           <t>2839</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>76,33%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>25,21%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>4802</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>2566</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6295</t>
-        </is>
-      </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10215</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -1400,112 +1400,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>20219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>29441</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>54</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>35396</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>29616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -1513,112 +1513,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29694</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -1856,112 +1856,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -1969,112 +1969,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13737</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -2312,112 +2312,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>25613</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>34588</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>77</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>43669</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>57426</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>70,18%</t>
         </is>
       </c>
     </row>
@@ -2425,112 +2425,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21408</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43009</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -2999,112 +2999,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -3112,112 +3112,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3333</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,22%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3469</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>52,13%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>453</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12411</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -3455,112 +3455,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10831</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>24617</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>25041</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25968</t>
+          <t>44901</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>38444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33242</t>
+          <t>52763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -3568,112 +3568,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25128</t>
+          <t>20827</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10273</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6071</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15715</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>13,52%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25041</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19862</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>31084</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>55,78%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>44,24%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>69,24%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>44901</t>
+          <t>25968</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37631</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51859</t>
+          <t>33078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>435</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -3911,42 +3911,42 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3956,67 +3956,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>10818</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>15288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>59,7%</t>
         </is>
       </c>
     </row>
@@ -4024,42 +4024,42 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4069,67 +4069,67 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>9843</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10698</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,59%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>16233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -4367,112 +4367,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>19123</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>31080</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>34859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>48560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>67174</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>31581</t>
+          <t>58216</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48464</t>
+          <t>76037</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -4480,112 +4480,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>41772</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34579</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48331</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>67174</t>
+          <t>39538</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57634</t>
+          <t>31462</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76231</t>
+          <t>48005</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -5054,17 +5054,17 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -5167,17 +5167,17 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -5510,112 +5510,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>15850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>26953</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>32695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>41789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -5623,112 +5623,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14021</t>
+          <t>738</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27315</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>37702</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32033</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41873</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -5966,17 +5966,17 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -6006,72 +6006,72 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -6079,17 +6079,17 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -6119,72 +6119,72 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -6422,112 +6422,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>76</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>45339</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>56135</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -6535,112 +6535,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20890</t>
+          <t>738</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34505</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>51282</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56366</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>430</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -7184,12 +7184,12 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -7222,7 +7222,7 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>652</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7262,47 +7262,47 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>652</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>425</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -7565,112 +7565,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>23284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -7678,112 +7678,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4291</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23318</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>400</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -8021,112 +8021,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -8134,112 +8134,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -8477,112 +8477,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>31444</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>35896</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -8590,112 +8590,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>2291</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>829</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35922</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP11C$ingresado-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP11C$ingresado-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -841,102 +841,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>74,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2918</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>19,59%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>70,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>71,41%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3722</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>21,26%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>74,79%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1478</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4244</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>21,26%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -944,112 +944,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>674</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>674</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -1057,112 +1057,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5215</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>737</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3754</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3604</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2069</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5721</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5546</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2623</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9767</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>26,45%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>2616</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5789</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>6090</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>12,43%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>27,51%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5546</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2814</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>10215</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>12902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -1400,112 +1400,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29616</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -1513,112 +1513,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>13554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>54</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>35396</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>41054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>70,82%</t>
         </is>
       </c>
     </row>
@@ -1635,107 +1635,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>488</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>32,54%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>488</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2804</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2867</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>41,46%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2666</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -1748,107 +1748,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3514</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>51,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3367</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3538</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>49,78%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3723</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -1856,112 +1856,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -1969,112 +1969,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>81,13%</t>
         </is>
       </c>
     </row>
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6149</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>737</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3891</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4416</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2557</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6043</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6890</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3440</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11266</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>24,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>3422</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7505</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>7413</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>9,69%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>6890</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3566</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>11877</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>16223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -2312,112 +2312,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21408</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25613</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24536</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34588</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43669</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57426</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>28,35%</t>
         </is>
       </c>
     </row>
@@ -2425,112 +2425,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>34526</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>77</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>43659</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>57555</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,102 +2783,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3747</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2666</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>67,21%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4223</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4436</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -2891,107 +2891,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>651</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3455</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>651</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2917</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3432</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>23,18%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -3009,102 +3009,102 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -3112,42 +3112,42 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3157,67 +3157,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3760</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8355</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1089</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3465</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3478</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2,87%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3760</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8006</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9364</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10807</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>24,07%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4584</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>3,44%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5821</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>10810</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -3455,112 +3455,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24617</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15695</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11079</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20479</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>41,36%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>53,96%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25041</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19412</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>30644</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,78%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>43,24%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>68,26%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44901</t>
+          <t>25968</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38444</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -3568,112 +3568,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>25041</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>19318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>30546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>14944</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>25968</t>
+          <t>44901</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19353</t>
+          <t>37713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>51995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5061</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>31,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1329</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3955</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>13,69%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>40,73%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1255</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5457</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2830</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3966</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3916</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2795</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -3911,112 +3911,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10698</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -4024,112 +4024,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14492</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>57,83%</t>
         </is>
       </c>
     </row>
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11146</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3093</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1104</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6523</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5952</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,98%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2626</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11425</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7359</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>12598</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>17,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>2236</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>6107</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5845</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7359</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3899</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>12435</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -4367,112 +4367,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31080</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41772</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34859</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48560</t>
+          <t>27200</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>67174</t>
+          <t>39538</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58216</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76037</t>
+          <t>47721</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -4480,112 +4480,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>34003</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27624</t>
+          <t>48513</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>19839</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24956</t>
+          <t>31517</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>67174</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31462</t>
+          <t>56997</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48005</t>
+          <t>75948</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5054,17 +5054,17 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -5167,17 +5167,17 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5273</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1740</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4235</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4703</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10,55%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1673</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5656</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -5402,79 +5402,79 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6817</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2406</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>6112</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
           <t>2407</t>
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -5510,112 +5510,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14021</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15850</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>738</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26953</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37702</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32695</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41789</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -5623,112 +5623,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>27365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>32342</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>41746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -5858,107 +5858,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>39,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2711</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>39,84%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2631</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -5966,112 +5966,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4126</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4182</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6167</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,46%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>30,3%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>90,63%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -6079,112 +6079,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>1641</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6175</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>61,46%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>24,12%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>90,74%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>4140</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>29,23%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>60,84%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5466</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1740</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4666</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4772</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,45%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1673</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5980</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -6314,92 +6314,92 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7259</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>17,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>3040</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6975</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -6422,112 +6422,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20890</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>738</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34525</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>51282</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56135</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -6535,112 +6535,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>30392</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25123</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>34515</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>22702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>76</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>44615</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>55531</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7109,87 +7109,87 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>39,74%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>67,19%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>756</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -7199,12 +7199,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>80,38%</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7232,77 +7232,77 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>32,81%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>626</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>592</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4237</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>30,86%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4641</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4522</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>11,75%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>42,12%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4790</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>335</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -7565,112 +7565,112 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>646</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23284</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -7678,112 +7678,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>19013</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>21870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>88,47%</t>
         </is>
       </c>
     </row>
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2902</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>39,31%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1151</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,79%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>66,36%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2853</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -7913,107 +7913,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5046</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>68,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4799</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6549</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>60,47%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5927</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -8021,112 +8021,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8134,112 +8134,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11712</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3505</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,75%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4493</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8384,12 +8384,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -8477,112 +8477,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Urgencias</t>
+          <t>Nada</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>646</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35896</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -8590,112 +8590,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Nada</t>
+          <t>Urgencias</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>29960</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>24237</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>33742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
